--- a/mod_project/data_tables/qol_party_skill_text.xlsx
+++ b/mod_project/data_tables/qol_party_skill_text.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Max HP increased. (Up to +100 at 50 awards)</t>
+          <t>Max HP increased (up to +100).</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -538,7 +538,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ATK increased. (Up to +32 at 50 awards)</t>
+          <t>ATK increased (up to +32).</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -579,7 +579,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Max TP and fire resistance increased. (Up to +50 and +20% at 50 awards)</t>
+          <t>Up to max TP +50 and fire resistance +20%.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -620,7 +620,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Slash resistance increased. (Up to +25% at 50 awards)</t>
+          <t>Slash resistance increased (up to +25%).</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -661,7 +661,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>INT increased. (Up to +20 at 50 awards)</t>
+          <t>INT increased (up to +20).</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -702,7 +702,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DEF increased. (Up to +25 at 50 awards)</t>
+          <t>DEF increased (up to +25).</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AGI increased. (Up to +20 at 50 awards)</t>
+          <t>AGI increased (up to +20).</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stab resistance increased. (Up to +20% at 50 awards)</t>
+          <t>Stab resistance increased (up to +20%).</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -825,7 +825,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Max HP and TP increased. (Up to +50 and +50 at 50 awards)</t>
+          <t>Max HP and TP increased (up to +50 each).</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RES increased. (Up to +20 at 50 awards)</t>
+          <t>RES increased (up to +20).</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -907,7 +907,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bash resistance increased. (Up to +20% at 50 awards)</t>
+          <t>Bash resistance increased (up to +20%).</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -948,7 +948,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>DEX increased. (Up to +32 at 50 awards)</t>
+          <t>DEX increased (up to +32).</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Water and earth resistance increased. (Up to +20% and +20% at 50 awards)</t>
+          <t>Up to water and earth resistance +20% each.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wind resistance and AGI increased. (Up to +20% and +10 at 50 awards)</t>
+          <t>Up to wind resistance +20% and AGI +10.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bash and earth resistance increased. (Up to +10% and +20% at 50 awards)</t>
+          <t>Up to bash resistance +10%, earth +20%.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lightning resistance and max HP increased. (Up to +20% and +50 at 50 awards)</t>
+          <t>Up to lightning resistance +20% and max HP +50.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fire resistance and ATK increased. (Up to +10% and +20 at 50 awards)</t>
+          <t>Up to fire resistance +10% and ATK +20.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>DEX and AGI increased. (Up to +20 and +20 at 50 awards)</t>
+          <t>DEX and AGI increased (up to +20 each).</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Max TP and fire resistance increased. (Up to +50 and +20% at 50 awards)</t>
+          <t>Up to max TP +50 and fire resistance +20%.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>

--- a/mod_project/data_tables/qol_party_skill_text.xlsx
+++ b/mod_project/data_tables/qol_party_skill_text.xlsx
@@ -579,7 +579,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Up to max TP +50 and fire resistance +20%.</t>
+          <t>Up to max TP +50 and fire resistance +20.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -588,7 +588,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>+50, +20%</t>
+          <t>+50, +20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Slash resistance increased (up to +25%).</t>
+          <t>Slash resistance increased (up to +25).</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -629,7 +629,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>+25%</t>
+          <t>+25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stab resistance increased (up to +20%).</t>
+          <t>Stab resistance increased (up to +20).</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bash resistance increased (up to +20%).</t>
+          <t>Bash resistance increased (up to +20).</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>+20%</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Up to water and earth resistance +20% each.</t>
+          <t>Up to water and earth resistance +20 each.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>+20%, +20%</t>
+          <t>+20, +20</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Up to wind resistance +20% and AGI +10.</t>
+          <t>Up to wind resistance +20 and AGI +10.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>+20%, +10</t>
+          <t>+20, +10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Up to bash resistance +10%, earth +20%.</t>
+          <t>Up to bash resistance +10, earth +20.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>+10%, +20%</t>
+          <t>+10, +20</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Up to lightning resistance +20% and max HP +50.</t>
+          <t>Up to lightning resistance +20 and max HP +50.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>+20%, +50</t>
+          <t>+20, +50</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Up to fire resistance +10% and ATK +20.</t>
+          <t>Up to fire resistance +10 and ATK +20.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>+10%, +20</t>
+          <t>+10, +20</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Up to max TP +50 and fire resistance +20%.</t>
+          <t>Up to max TP +50 and fire resistance +20.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>+50, +20%</t>
+          <t>+50, +20</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">

--- a/mod_project/data_tables/qol_party_skill_text.xlsx
+++ b/mod_project/data_tables/qol_party_skill_text.xlsx
@@ -1030,17 +1030,21 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lightning resistance increased.</t>
+          <t>Lightning resistance increased (up to +50).</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>373</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>+50</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>The wiki gives no figure</t>
+          <t>exe-verified (0x4f92f4)</t>
         </is>
       </c>
     </row>
